--- a/data/valuations/IVN_TO/IVN_TO_modelo_valoracion.xlsx
+++ b/data/valuations/IVN_TO/IVN_TO_modelo_valoracion.xlsx
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.36</v>
+        <v>0.036</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.28</v>
+        <v>0.028</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.24</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="9">
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.52</v>
+        <v>0.055</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.468</v>
+        <v>0.0495</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.416</v>
+        <v>0.044</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.364</v>
+        <v>0.0385</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.312</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="10">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.28</v>
+        <v>0.025</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.2520000000000001</v>
+        <v>0.0225</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.224</v>
+        <v>0.02</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.196</v>
+        <v>0.0175</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.168</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="11">
@@ -844,19 +844,19 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.9328271266345965</v>
+        <v>0.01</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.9328271266345965</v>
+        <v>0.01</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.9328271266345965</v>
+        <v>0.01</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.9328271266345965</v>
+        <v>0.01</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.9328271266345965</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.9228271266345965</v>
+        <v>0.01</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.9228271266345965</v>
+        <v>0.01</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.9228271266345965</v>
+        <v>0.01</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.9228271266345965</v>
+        <v>0.01</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.9228271266345965</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="22">
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.9428271266345966</v>
+        <v>0.01</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.9428271266345966</v>
+        <v>0.01</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.9428271266345966</v>
+        <v>0.01</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.9428271266345966</v>
+        <v>0.01</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.9428271266345966</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="23">
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1349</v>
+        <v>0.1306</v>
       </c>
     </row>
     <row r="36">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.1249</v>
+        <v>0.1206</v>
       </c>
     </row>
     <row r="37">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1549</v>
+        <v>0.1406</v>
       </c>
     </row>
     <row r="38">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>11.59</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="4">
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="I21" s="8">
-        <f>I12*$C$16</f>
+        <f>I8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/11.59-1</f>
+        <f>C33/11.13-1</f>
         <v/>
       </c>
     </row>
@@ -3301,176 +3301,176 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.1049</v>
+        <v>0.1006</v>
       </c>
       <c r="C39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$12*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$12*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$12*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$12*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$12*16/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.1149</v>
+        <v>0.1106</v>
       </c>
       <c r="C40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$12*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$12*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$12*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$12*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$12*16/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.1249</v>
+        <v>0.1206</v>
       </c>
       <c r="C41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$12*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$12*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$12*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$12*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$12*16/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1349</v>
+        <v>0.1306</v>
       </c>
       <c r="C42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$12*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$12*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$12*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$12*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$12*16/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1449</v>
+        <v>0.1406</v>
       </c>
       <c r="C43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$12*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$12*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$12*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$12*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$12*16/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1549</v>
+        <v>0.1506</v>
       </c>
       <c r="C44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$12*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$12*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$12*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$12*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$12*16/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1649</v>
+        <v>0.1606</v>
       </c>
       <c r="C45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$12*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$12*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$12*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$12*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$12*16/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/IVN_TO/IVN_TO_modelo_valoracion.xlsx
+++ b/data/valuations/IVN_TO/IVN_TO_modelo_valoracion.xlsx
@@ -517,7 +517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ivanhoe Mines Ltd. (IVN.TO) - Assumptions</t>
+          <t>Ivanhoe Mines Ltd. (IVN_TO) - Assumptions</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -844,19 +844,19 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3115598428495409</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3115598428495409</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3115598428495409</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3115598428495409</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3115598428495409</v>
       </c>
     </row>
     <row r="21">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3065598428495409</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3065598428495409</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3065598428495409</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3065598428495409</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3065598428495409</v>
       </c>
     </row>
     <row r="22">
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3165598428495409</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3165598428495409</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3165598428495409</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3165598428495409</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.3165598428495409</v>
       </c>
     </row>
     <row r="23">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1306</v>
+        <v>0.1358</v>
       </c>
     </row>
     <row r="36">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.1206</v>
+        <v>0.1258</v>
       </c>
     </row>
     <row r="37">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1406</v>
+        <v>0.1458</v>
       </c>
     </row>
     <row r="38">
@@ -1215,7 +1215,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ivanhoe Mines Ltd. (IVN.TO) - Historical Financial Statements</t>
+          <t>Ivanhoe Mines Ltd. (IVN_TO) - Historical Financial Statements</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1701,7 +1701,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ivanhoe Mines Ltd. (IVN.TO) - Financial Model</t>
+          <t>Ivanhoe Mines Ltd. (IVN_TO) - Financial Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2811,7 +2811,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ivanhoe Mines Ltd. (IVN.TO) - DCF Valuation</t>
+          <t>Ivanhoe Mines Ltd. (IVN_TO) - DCF Valuation</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>11.13</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="4">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/11.13-1</f>
+        <f>C33/10.44-1</f>
         <v/>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.1006</v>
+        <v>0.1058</v>
       </c>
       <c r="C39" s="22">
         <f>(E$12/(1+$A$39)^1+F$12/(1+$A$39)^2+G$12/(1+$A$39)^3+H$12/(1+$A$39)^4+I$12/(1+$A$39)^5+I$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3326,7 +3326,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.1106</v>
+        <v>0.1158</v>
       </c>
       <c r="C40" s="22">
         <f>(E$12/(1+$A$40)^1+F$12/(1+$A$40)^2+G$12/(1+$A$40)^3+H$12/(1+$A$40)^4+I$12/(1+$A$40)^5+I$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3351,7 +3351,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.1206</v>
+        <v>0.1258</v>
       </c>
       <c r="C41" s="22">
         <f>(E$12/(1+$A$41)^1+F$12/(1+$A$41)^2+G$12/(1+$A$41)^3+H$12/(1+$A$41)^4+I$12/(1+$A$41)^5+I$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1306</v>
+        <v>0.1358</v>
       </c>
       <c r="C42" s="22">
         <f>(E$12/(1+$A$42)^1+F$12/(1+$A$42)^2+G$12/(1+$A$42)^3+H$12/(1+$A$42)^4+I$12/(1+$A$42)^5+I$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3401,7 +3401,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1406</v>
+        <v>0.1458</v>
       </c>
       <c r="C43" s="22">
         <f>(E$12/(1+$A$43)^1+F$12/(1+$A$43)^2+G$12/(1+$A$43)^3+H$12/(1+$A$43)^4+I$12/(1+$A$43)^5+I$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1506</v>
+        <v>0.1558</v>
       </c>
       <c r="C44" s="22">
         <f>(E$12/(1+$A$44)^1+F$12/(1+$A$44)^2+G$12/(1+$A$44)^3+H$12/(1+$A$44)^4+I$12/(1+$A$44)^5+I$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1606</v>
+        <v>0.1658</v>
       </c>
       <c r="C45" s="22">
         <f>(E$12/(1+$A$45)^1+F$12/(1+$A$45)^2+G$12/(1+$A$45)^3+H$12/(1+$A$45)^4+I$12/(1+$A$45)^5+I$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
